--- a/card disdoc.xlsx
+++ b/card disdoc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5a34dfa97c331738/Documents/ilja/Unity/ld60/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{0C438EE4-F750-43B6-8F91-DB4328E051E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05F89271-371A-43DD-9E9A-37E207AAB8E3}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{0C438EE4-F750-43B6-8F91-DB4328E051E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7792547F-D58E-4035-BEC4-A976F3B0218E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{B625C734-B299-4013-86DD-D50F51382B50}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="59">
   <si>
     <t>Hand (pts)</t>
   </si>
@@ -164,12 +164,6 @@
     <t>gain aditional reroll</t>
   </si>
   <si>
-    <t>Count</t>
-  </si>
-  <si>
-    <t>count: 1 if no value entered</t>
-  </si>
-  <si>
     <t>gain additional dice. Loose 1 reroll</t>
   </si>
   <si>
@@ -219,6 +213,9 @@
   </si>
   <si>
     <t>five of a kind grants bonus 200 points</t>
+  </si>
+  <si>
+    <t>Visuals</t>
   </si>
 </sst>
 </file>
@@ -1074,7 +1071,7 @@
         <v>27</v>
       </c>
       <c r="N14" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="O14" t="s">
         <v>29</v>
@@ -1087,9 +1084,6 @@
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="N15">
-        <v>2</v>
-      </c>
       <c r="O15">
         <v>0</v>
       </c>
@@ -1098,9 +1092,6 @@
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="K16" t="s">
-        <v>42</v>
-      </c>
       <c r="O16">
         <v>1</v>
       </c>
@@ -1121,7 +1112,7 @@
         <v>3</v>
       </c>
       <c r="P18" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="15:17" x14ac:dyDescent="0.25">
@@ -1129,7 +1120,7 @@
         <v>4</v>
       </c>
       <c r="P19" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q19" t="s">
         <v>37</v>
@@ -1156,7 +1147,7 @@
         <v>7</v>
       </c>
       <c r="P22" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23" spans="15:17" x14ac:dyDescent="0.25">
@@ -1164,7 +1155,7 @@
         <v>8</v>
       </c>
       <c r="P23" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24" spans="15:17" x14ac:dyDescent="0.25">
@@ -1172,7 +1163,7 @@
         <v>9</v>
       </c>
       <c r="P24" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25" spans="15:17" x14ac:dyDescent="0.25">
@@ -1180,7 +1171,7 @@
         <v>10</v>
       </c>
       <c r="P25" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="15:17" x14ac:dyDescent="0.25">
@@ -1188,7 +1179,7 @@
         <v>11</v>
       </c>
       <c r="P26" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="15:17" x14ac:dyDescent="0.25">
@@ -1196,7 +1187,7 @@
         <v>12</v>
       </c>
       <c r="P27" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28" spans="15:17" x14ac:dyDescent="0.25">
@@ -1204,7 +1195,7 @@
         <v>13</v>
       </c>
       <c r="P28" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29" spans="15:17" x14ac:dyDescent="0.25">
@@ -1212,7 +1203,7 @@
         <v>14</v>
       </c>
       <c r="P29" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30" spans="15:17" x14ac:dyDescent="0.25">
@@ -1220,7 +1211,7 @@
         <v>15</v>
       </c>
       <c r="P30" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="31" spans="15:17" x14ac:dyDescent="0.25">
@@ -1228,7 +1219,7 @@
         <v>16</v>
       </c>
       <c r="P31" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="32" spans="15:17" x14ac:dyDescent="0.25">
@@ -1236,7 +1227,7 @@
         <v>17</v>
       </c>
       <c r="P32" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="33" spans="15:16" x14ac:dyDescent="0.25">
@@ -1244,7 +1235,7 @@
         <v>18</v>
       </c>
       <c r="P33" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="34" spans="15:16" x14ac:dyDescent="0.25">
@@ -1252,7 +1243,7 @@
         <v>19</v>
       </c>
       <c r="P34" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="35" spans="15:16" x14ac:dyDescent="0.25">
@@ -1260,7 +1251,7 @@
         <v>20</v>
       </c>
       <c r="P35" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="36" spans="15:16" x14ac:dyDescent="0.25">
@@ -1268,7 +1259,7 @@
         <v>21</v>
       </c>
       <c r="P36" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="37" spans="15:16" x14ac:dyDescent="0.25">

--- a/card disdoc.xlsx
+++ b/card disdoc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5a34dfa97c331738/Documents/ilja/Unity/ld60/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{0C438EE4-F750-43B6-8F91-DB4328E051E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7792547F-D58E-4035-BEC4-A976F3B0218E}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{0C438EE4-F750-43B6-8F91-DB4328E051E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD10BA0D-C272-4219-ACA5-30348B3B0356}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{B625C734-B299-4013-86DD-D50F51382B50}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="78">
   <si>
     <t>Hand (pts)</t>
   </si>
@@ -216,6 +216,63 @@
   </si>
   <si>
     <t>Visuals</t>
+  </si>
+  <si>
+    <t>44 / 44</t>
+  </si>
+  <si>
+    <t>66 / 66</t>
+  </si>
+  <si>
+    <t>88 / 88</t>
+  </si>
+  <si>
+    <t>65 / 57</t>
+  </si>
+  <si>
+    <t>93 / 86</t>
+  </si>
+  <si>
+    <t>120 / 114</t>
+  </si>
+  <si>
+    <t>82 / 75</t>
+  </si>
+  <si>
+    <t>116 / 112</t>
+  </si>
+  <si>
+    <t>147 / 145</t>
+  </si>
+  <si>
+    <t>3 (current)</t>
+  </si>
+  <si>
+    <t>97 / 92</t>
+  </si>
+  <si>
+    <t>137 / 135</t>
+  </si>
+  <si>
+    <t>172 / 171</t>
+  </si>
+  <si>
+    <t>112 / 109</t>
+  </si>
+  <si>
+    <t>157 / 157</t>
+  </si>
+  <si>
+    <t>192 / 191</t>
+  </si>
+  <si>
+    <t>126 / 125</t>
+  </si>
+  <si>
+    <t>174 / 173</t>
+  </si>
+  <si>
+    <t>206 / 204</t>
   </si>
 </sst>
 </file>
@@ -1099,7 +1156,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="17" spans="15:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
       <c r="O17">
         <v>2</v>
       </c>
@@ -1107,7 +1164,19 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="15:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="O18">
         <v>3</v>
       </c>
@@ -1115,7 +1184,19 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="15:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B19" s="2">
+        <v>0</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="O19">
         <v>4</v>
       </c>
@@ -1126,7 +1207,19 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="15:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B20" s="2">
+        <v>1</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="O20">
         <v>5</v>
       </c>
@@ -1134,7 +1227,19 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="15:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B21" s="2">
+        <v>2</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>67</v>
+      </c>
       <c r="O21">
         <v>6</v>
       </c>
@@ -1142,7 +1247,19 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="15:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="B22" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>71</v>
+      </c>
       <c r="O22">
         <v>7</v>
       </c>
@@ -1150,7 +1267,19 @@
         <v>41</v>
       </c>
     </row>
-    <row r="23" spans="15:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B23" s="2">
+        <v>4</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>74</v>
+      </c>
       <c r="O23">
         <v>8</v>
       </c>
@@ -1158,7 +1287,19 @@
         <v>44</v>
       </c>
     </row>
-    <row r="24" spans="15:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B24" s="2">
+        <v>5</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>77</v>
+      </c>
       <c r="O24">
         <v>9</v>
       </c>
@@ -1166,7 +1307,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="25" spans="15:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:17" x14ac:dyDescent="0.25">
       <c r="O25">
         <v>10</v>
       </c>
@@ -1174,7 +1315,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="26" spans="15:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:17" x14ac:dyDescent="0.25">
       <c r="O26">
         <v>11</v>
       </c>
@@ -1182,7 +1323,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="15:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:17" x14ac:dyDescent="0.25">
       <c r="O27">
         <v>12</v>
       </c>
@@ -1190,7 +1331,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="15:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:17" x14ac:dyDescent="0.25">
       <c r="O28">
         <v>13</v>
       </c>
@@ -1198,7 +1339,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="29" spans="15:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:17" x14ac:dyDescent="0.25">
       <c r="O29">
         <v>14</v>
       </c>
@@ -1206,7 +1347,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="30" spans="15:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:17" x14ac:dyDescent="0.25">
       <c r="O30">
         <v>15</v>
       </c>
@@ -1214,7 +1355,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="31" spans="15:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:17" x14ac:dyDescent="0.25">
       <c r="O31">
         <v>16</v>
       </c>
@@ -1222,7 +1363,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="32" spans="15:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:17" x14ac:dyDescent="0.25">
       <c r="O32">
         <v>17</v>
       </c>

--- a/card disdoc.xlsx
+++ b/card disdoc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5a34dfa97c331738/Documents/ilja/Unity/ld60/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{0C438EE4-F750-43B6-8F91-DB4328E051E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD10BA0D-C272-4219-ACA5-30348B3B0356}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="8_{0C438EE4-F750-43B6-8F91-DB4328E051E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F79F98E-08A1-4642-AE75-3DCA3B84840C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{B625C734-B299-4013-86DD-D50F51382B50}"/>
   </bookViews>
@@ -143,9 +143,6 @@
     <t>Effect</t>
   </si>
   <si>
-    <t xml:space="preserve"> each 1 grants 3 bonus points</t>
-  </si>
-  <si>
     <t>you may reroll 4 any number of times (right click)</t>
   </si>
   <si>
@@ -158,66 +155,18 @@
     <t xml:space="preserve">you can flip (right click) 2 to gain 5 and wiseverse any number of times </t>
   </si>
   <si>
-    <t>1 1 1 multiplies combination's point count by 1.67</t>
-  </si>
-  <si>
     <t>gain aditional reroll</t>
   </si>
   <si>
     <t>gain additional dice. Loose 1 reroll</t>
   </si>
   <si>
-    <t>street multiplies points count by 2</t>
-  </si>
-  <si>
     <t>1 1 grants 52 bonus points</t>
   </si>
   <si>
-    <t>2 2 grants bonus 33 points</t>
-  </si>
-  <si>
-    <t>3 3 grants bonus 33 points</t>
-  </si>
-  <si>
-    <t>you can destroy (right click) 6 to gain additional reroll</t>
-  </si>
-  <si>
-    <t>6 6 6 grants bonus 67 points</t>
-  </si>
-  <si>
-    <t>5 5 5 grants bonus 70 points</t>
-  </si>
-  <si>
-    <t>4 4 4 grants bonus 90 points</t>
-  </si>
-  <si>
-    <t>1 6 grants bonus 20 points</t>
-  </si>
-  <si>
-    <t>3 4 grants bonus 20 points</t>
-  </si>
-  <si>
-    <t>2 5 grants bonus 20 points</t>
-  </si>
-  <si>
-    <t>odd dices grant bonus 7 points</t>
-  </si>
-  <si>
     <t>result multiplies by 2 if all dices are even</t>
   </si>
   <si>
-    <t>full house grants bonus 67 points</t>
-  </si>
-  <si>
-    <t>four of the kind grants bonus 100 points</t>
-  </si>
-  <si>
-    <t>five of a kind grants bonus 200 points</t>
-  </si>
-  <si>
-    <t>Visuals</t>
-  </si>
-  <si>
     <t>44 / 44</t>
   </si>
   <si>
@@ -273,6 +222,57 @@
   </si>
   <si>
     <t>206 / 204</t>
+  </si>
+  <si>
+    <t>odd dices grant bonus 0.2 multiplier</t>
+  </si>
+  <si>
+    <t>1 6 grants 1.5 multiplier</t>
+  </si>
+  <si>
+    <t>2 5 grants bonus 67 points</t>
+  </si>
+  <si>
+    <t>you can destroy (right click) 6 to gain additional reroll and 0.5 multiplier</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> each 1 grants 10 bonus points</t>
+  </si>
+  <si>
+    <t>full house grants bonus 100 points</t>
+  </si>
+  <si>
+    <t>four of the kind grants bonus 167 points</t>
+  </si>
+  <si>
+    <t>five of a kind grants bonus 333 points</t>
+  </si>
+  <si>
+    <t>street multiplies grants 2 multiplier</t>
+  </si>
+  <si>
+    <t>6 6 6 grants bonus 100 points</t>
+  </si>
+  <si>
+    <t>5 5 5 grants bonus 100 points</t>
+  </si>
+  <si>
+    <t>4 4 4 grants bonus 100 points</t>
+  </si>
+  <si>
+    <t>2 2 grants bonus 0.25 multiplier</t>
+  </si>
+  <si>
+    <t>3 3 grants bonus 67 points</t>
+  </si>
+  <si>
+    <t>3 4 grants bonus 0.25 multiplier</t>
+  </si>
+  <si>
+    <t>1 1 1 multiplies combination's point count by 2</t>
+  </si>
+  <si>
+    <t>1 2 3 grants 50 points and 1 additional reroll next round</t>
   </si>
 </sst>
 </file>
@@ -348,6 +348,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1127,9 +1131,6 @@
       <c r="C14" t="s">
         <v>27</v>
       </c>
-      <c r="N14" t="s">
-        <v>58</v>
-      </c>
       <c r="O14" t="s">
         <v>29</v>
       </c>
@@ -1137,7 +1138,7 @@
         <v>33</v>
       </c>
       <c r="Q14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -1145,7 +1146,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
@@ -1153,7 +1154,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.25">
@@ -1161,7 +1162,7 @@
         <v>2</v>
       </c>
       <c r="P17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="2:17" x14ac:dyDescent="0.25">
@@ -1181,7 +1182,7 @@
         <v>3</v>
       </c>
       <c r="P18" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.25">
@@ -1189,22 +1190,22 @@
         <v>0</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="O19">
         <v>4</v>
       </c>
       <c r="P19" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="Q19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.25">
@@ -1212,19 +1213,19 @@
         <v>1</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="O20">
         <v>5</v>
       </c>
       <c r="P20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="2:17" x14ac:dyDescent="0.25">
@@ -1232,39 +1233,39 @@
         <v>2</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="O21">
         <v>6</v>
       </c>
       <c r="P21" t="s">
-        <v>39</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" spans="2:17" ht="30" x14ac:dyDescent="0.25">
       <c r="B22" s="5" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="O22">
         <v>7</v>
       </c>
       <c r="P22" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23" spans="2:17" x14ac:dyDescent="0.25">
@@ -1272,19 +1273,19 @@
         <v>4</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="O23">
         <v>8</v>
       </c>
       <c r="P23" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24" spans="2:17" x14ac:dyDescent="0.25">
@@ -1292,19 +1293,19 @@
         <v>5</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="O24">
         <v>9</v>
       </c>
       <c r="P24" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25" spans="2:17" x14ac:dyDescent="0.25">
@@ -1312,7 +1313,7 @@
         <v>10</v>
       </c>
       <c r="P25" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26" spans="2:17" x14ac:dyDescent="0.25">
@@ -1320,7 +1321,7 @@
         <v>11</v>
       </c>
       <c r="P26" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27" spans="2:17" x14ac:dyDescent="0.25">
@@ -1328,7 +1329,7 @@
         <v>12</v>
       </c>
       <c r="P27" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28" spans="2:17" x14ac:dyDescent="0.25">
@@ -1336,7 +1337,7 @@
         <v>13</v>
       </c>
       <c r="P28" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29" spans="2:17" x14ac:dyDescent="0.25">
@@ -1344,7 +1345,7 @@
         <v>14</v>
       </c>
       <c r="P29" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
     </row>
     <row r="30" spans="2:17" x14ac:dyDescent="0.25">
@@ -1352,7 +1353,7 @@
         <v>15</v>
       </c>
       <c r="P30" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
     </row>
     <row r="31" spans="2:17" x14ac:dyDescent="0.25">
@@ -1360,7 +1361,7 @@
         <v>16</v>
       </c>
       <c r="P31" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
     </row>
     <row r="32" spans="2:17" x14ac:dyDescent="0.25">
@@ -1368,7 +1369,7 @@
         <v>17</v>
       </c>
       <c r="P32" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33" spans="15:16" x14ac:dyDescent="0.25">
@@ -1376,7 +1377,7 @@
         <v>18</v>
       </c>
       <c r="P33" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
     </row>
     <row r="34" spans="15:16" x14ac:dyDescent="0.25">
@@ -1384,7 +1385,7 @@
         <v>19</v>
       </c>
       <c r="P34" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
     </row>
     <row r="35" spans="15:16" x14ac:dyDescent="0.25">
@@ -1392,7 +1393,7 @@
         <v>20</v>
       </c>
       <c r="P35" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
     </row>
     <row r="36" spans="15:16" x14ac:dyDescent="0.25">
@@ -1400,12 +1401,15 @@
         <v>21</v>
       </c>
       <c r="P36" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
     </row>
     <row r="37" spans="15:16" x14ac:dyDescent="0.25">
       <c r="O37">
         <v>22</v>
+      </c>
+      <c r="P37" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="38" spans="15:16" x14ac:dyDescent="0.25">

--- a/card disdoc.xlsx
+++ b/card disdoc.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5a34dfa97c331738/Documents/ilja/Unity/ld60/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="8_{0C438EE4-F750-43B6-8F91-DB4328E051E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F79F98E-08A1-4642-AE75-3DCA3B84840C}"/>
+  <xr:revisionPtr revIDLastSave="96" documentId="8_{0C438EE4-F750-43B6-8F91-DB4328E051E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FCCEF6DF-AD37-4E9B-9F21-5377E52F86E6}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{B625C734-B299-4013-86DD-D50F51382B50}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{B625C734-B299-4013-86DD-D50F51382B50}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Cards" sheetId="1" r:id="rId1"/>
+    <sheet name="Writing" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="103">
   <si>
     <t>Hand (pts)</t>
   </si>
@@ -273,6 +274,317 @@
   </si>
   <si>
     <t>1 2 3 grants 50 points and 1 additional reroll next round</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Speaker </t>
+  </si>
+  <si>
+    <t>Bad</t>
+  </si>
+  <si>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t>Hopefull</t>
+  </si>
+  <si>
+    <t>Text</t>
+  </si>
+  <si>
+    <t>Mom</t>
+  </si>
+  <si>
+    <t>Friend</t>
+  </si>
+  <si>
+    <t>Info:</t>
+  </si>
+  <si>
+    <t>1 - player</t>
+  </si>
+  <si>
+    <t>2- another speaker</t>
+  </si>
+  <si>
+    <t>1 - hi mom...
+2 - Oh god, darling, where are you missing for so long?
+1 - Eh... Mom, I want to ask you...
+2 - Dont ask me, answer my question first! I am so worried...
+1 - Mom, I am fine, just trust me...
+2 - Where are you? Please...
+1 - ...
+1 - I am at metro station. I am finally coming home.
+2 - Oh god, dont make me so scared never again!
+2 - How long havent we met?
+1 - Mom, I want to ask you something...
+2 - You will ask me at home darling.
+2 - Oh god, its like second christmas
+2 - I should cook something very special for you!
+2 - What would you like? Ribs? Steak? Your favourite soup? Anything!
+1 - ...
+1 - Ribs would be fine...
+2 - I am so happy to hear you again!
+2 - See you soon darling! Bye!
+1 - Bye mom... (end call)</t>
+  </si>
+  <si>
+    <t>If text of the speaker is in brackets, out it in itallic and do not remove brackets. It is like thoughts of character</t>
+  </si>
+  <si>
+    <t>1 - hi mom...
+2 - Oh god, darling, where are you missing for so long?
+1 - Eh... Mom, I want to ask you something.
+1 - What would you do, if I died? 
+2 - Oh god, darling, you are scaring me!
+2 - You dissapeared for 1 whole month, and now you are asking such wierd question!
+1 - Mom, really, what would you do? 
+2 - Oh god, darling, you are the most precious thing in my life!
+2 - How I suppoused to image my life without you?
+1 - (But you have been leaving for 1 month without me just as fine)
+2 - Hello?
+1 - Yeah, I am just hinking...
+2 - Please, come back home darling. I will cook your favorite dishes everyday! Please, just return!
+1 - I will, mom... (end call)</t>
+  </si>
+  <si>
+    <t>1 - hi mom...
+2 - Oh god, darling, where are you missing for so long?
+1 - Eh... Mom, I want to ask you something.
+1 - What would you do, if I died? 
+2 - Oh god, darling, you are scaring me!
+2 - You dissapeared for 1 whole month, and now you are asking such wierd question!
+1 - Mom, really, what would you do? 
+2 - Darling, please, stop all this "games"
+2 - Please, come back home. Dad and I are really worrying about you!
+1 - Do not even mention him...
+2 - ...
+2 - Darling, please, come ba... (end call...)
+1 - ...
+1 - Now,l she hates me too...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - Hi...
+2 - Yo, long time no see
+2 - I even thought you had died or something
+1 - Yeah, I am just about to ask...
+2 - All we was thinking like so lol
+2 - Your mom even came in front of ma doors in tears asking about you
+1 - Yeah... Lets not talk about this...
+2 - Gosh, what we should talk about in this case? 
+2 - I am so excited to hear your voice once again! 
+1 - I want to ask you...
+2 - The riddles you left before you dissapear
+1 - Huh? The riddles?
+2 - Yeah, I tried really hard on them
+1 - Oh, really? 
+2 - Yeah... But, gosh, did you even test them?
+2- They looks impossible! 
+1 - Oh, really...
+2 - Next time before creating new ones ask me for help first! I will definitelly create some thing award winning or i dunno.
+2 - I there are any competitions for riddles and puzzles of course...
+1 - Oh, yeah, sure...
+2 - When will you come back? 
+1- I will... (end call)
+</t>
+  </si>
+  <si>
+    <t>1 - Hi...
+2 - Yo, long time no see
+2 - I even thought you had died or something
+1 - Yeah, I am just about to ask...
+2 - All we was thinking like so lol
+2 - Your mom even came in front of ma doors in tears asking about you
+1 - Yeah... Lets not talk about this...
+1 - I want to ask you something?
+2 - You call me only when you are in trouble, rgiht?
+1 - Ah, no...
+1 - What would do, if I died?
+2 - ...
+2 - What? 
+1 - Seriously
+2 - I dunno. Maybe play fortnite as ussualy. Why do you asking?
+1 - Nevermind... (end call)</t>
+  </si>
+  <si>
+    <t>gf</t>
+  </si>
+  <si>
+    <t>Father</t>
+  </si>
+  <si>
+    <t>1 - Hi Honey
+2 - ...
+2 - Why are you calling?
+1 - Honey, dont be mad, I just want you ask ask something...
+2 - Dont be mad? 
+2 - Nobody havent seen you for 1 month, and now you calling me out of nothere to "ask me something"?
+1 - ...
+1 - Yeah...
+2 - you dissapeard like you havent existed at all, 
+2 - And the only thing that left from you was a bunch of stupid riddles...
+2 - How I suppoused to act? Huh? 
+1 - ...
+1 - The riddles, they would guide there i was...
+2 - Dont you find this very selfish? 
+1 - I do...
+2 - What you have become...
+1 - Honey, can I still ask you something?
+2 - ...
+2 - Go for it...
+1 - What would you do, if i died?
+2 - ...
+2 - ...
+2 - ...
+2 - You better die already (call end)</t>
+  </si>
+  <si>
+    <t>1 - Hi...
+2 - Yo, long time no see
+2 - I even thought you had died or something
+1 - Yeah, I am just about to ask...
+2 - All we was thinking like so lol
+2 - Your mom even came in front of ma doors in tears asking about you
+1 - Yeah... Lets not talk about this...
+1 - I want to ask you something?
+1 - What would do, if I died?
+2 - ...
+2 - I...
+1 - Seriously
+2 - What I soppoused to answer? 
+1 - I dont know. The first thing on your mind.
+2 - I dunno...
+2 - But i would be really sad about you...
+2 - Is everything good with you?
+1 - ...
+1 - By the way, have you solved the riddles?
+2 - Riddles? These that you have left before dissapearence?
+2 - Gosh, actually, no, they are too hard to be honest...
+1 - (you didnt even try) (endcall)</t>
+  </si>
+  <si>
+    <t>1 - Hi Honey
+2 - ...
+2 - Why are you calling?
+1 - Honey, dont be mad, I just want you ask ask something...
+2 - Dont be mad? 
+2 - Nobody havent seen you for 1 month, and now you calling me out of nothere to "ask me something"?
+1 - ...
+1 - Yeah...
+2 - you dissapeard like you havent existed at all, 
+2 - And the only thing that left from you was a bunch of stupid riddles...
+1 - ...
+1 - can i still ask you something?
+2 - Babe.
+2 - Just know, that I still love you
+2 - No matter what
+2 - Please, come back.
+2 - Everyone is so worried about you
+2 - Hope you are doing ok (call end)
+1 - (i love you too, honey)</t>
+  </si>
+  <si>
+    <t>2 - Hello?
+1 - Hi dad...
+2 - I thought you are dead...
+1 - As you see, i am not, haha
+2 - ...
+2 - Why are you calling?
+1 - Dad, I want you to ask something?
+2 - Lets talk about where is my vynil player first
+1 - Oh... It right in front of me, dont by worried...
+2 - Why did you take it...
+2 - When you left, you took nothing but my grandfather's vynil player and rifle...
+1 - Do you remmber, what I have told you about it?
+2 - you told me many stupid things
+1 - If I had funerals, I wanted this player to play that very song
+2 - So you are planning to blow your head of, rgiht?
+1 - ...
+2 - ...
+1 - Can I still ask you something?
+2 - go for it
+1 - If I died, what would you do?
+2 - ...
+2 - Send me your location, I will took back my things (endcall)
+1 - ...</t>
+  </si>
+  <si>
+    <t>1 - Hi Honey
+2 - ...
+2 - Why are you calling?
+1 - Honey, dont be mad, I just want you ask ask something...
+2 - Dont be mad? 
+2 - Nobody havent seen you for 1 month, and now you calling me out of nothere to "ask me something"?
+1 - ...
+1 - Yeah...
+2 - you dissapeard like you havent existed at all, 
+2 - And the only thing that left from you was a bunch of stupid riddles...
+1 - ...
+1 - can i still ask you something?
+2 - ...
+2 - Fine, go for it
+1 - What would you do, if i died?
+2 - ...
+2 - We can discuss it, when you finally come back
+2 - I still love you (end call)
+1 - (it better be a lie)</t>
+  </si>
+  <si>
+    <t>2 - Hello?
+1 - Hi dad...
+2 - I thought you are dead...
+1 - As you see, i am not, haha
+2 - ...
+2 - Why are you calling?
+1 - Dad, I want you to ask something?
+2 - Lets talk about where is my vynil player first
+1 - Oh... It right in front of me, dont by worried...
+2 - Why did you take it...
+2 - When you left, you took nothing but my grandfather's vynil player and rifle...
+1 - Do you remmber, what I have told you about it?
+2 - you told me many stupid things
+1 - If I had funerals, I wanted this player to play that very song
+2 - So you are planning to blow your head of, rgiht?
+1 - ...
+2 - ...
+1 - Can I still ask you something?
+2 - go for it
+1 - If I died, what would you do?
+2 - ...
+2 - No matter what you are thinking of us, but we really hoping you will come back home
+1 - its better be a lie (call end)</t>
+  </si>
+  <si>
+    <t>2 - Hello?
+1 - Hi dad...
+2 - I thought you are dead...
+1 - As you see, i am not, haha
+2 - ...
+2 - Why are you calling?
+1 - Dad, I want you to ask something?
+2 - Lets talk about where is my vynil player first
+1 - Oh... It right in front of me, dont by worried...
+2 - Why did you take it...
+2 - When you left, you took nothing but my grandfather's vynil player and rifle...
+1 - Do you remmber, what I have told you about it?
+2 - you told me many stupid things
+1 - If I had funerals, I wanted this player to play that very song
+2 - So you are planning to blow your head of, rgiht?
+1 - ...
+2 - ...
+1 - Can I still ask you something?
+2 - go for it
+1 - If I died, what would you do?
+2 - ...
+2 - I dont know why you hate me
+2 - Maybe I was to rough on you or something
+2 - But, just so know
+2 - Anything I did, I thought it would be better you 
+2 - And I am sorry for all the pain I caused...
+2 - Can i ask you something too?
+1 - Okay...
+2 - Do you still love us?
+1- ...
+2 - If you do, please, come back home (end call)</t>
   </si>
 </sst>
 </file>
@@ -316,7 +628,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -332,6 +644,18 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1500,4 +1824,248 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10006A7A-F87C-4A54-AC2B-0B8DC3F5EB25}">
+  <dimension ref="A1:L13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="6"/>
+      <c r="B1" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+    </row>
+    <row r="2" spans="1:12" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="L2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3" s="7"/>
+      <c r="C3" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="L3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4" s="7"/>
+      <c r="C4" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="L4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="L5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" s="7"/>
+      <c r="C6" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+    </row>
+    <row r="7" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B7" s="7"/>
+      <c r="C7" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+    </row>
+    <row r="8" spans="1:12" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+    </row>
+    <row r="9" spans="1:12" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B9" s="7"/>
+      <c r="C9" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+    </row>
+    <row r="10" spans="1:12" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B10" s="7"/>
+      <c r="C10" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+    </row>
+    <row r="11" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+    </row>
+    <row r="12" spans="1:12" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B12" s="7"/>
+      <c r="C12" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+    </row>
+    <row r="13" spans="1:12" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" s="7"/>
+      <c r="C13" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="17">
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="C8:I8"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="C10:I10"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="C11:I11"/>
+    <mergeCell ref="C12:I12"/>
+    <mergeCell ref="C13:I13"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="C2:I2"/>
+    <mergeCell ref="C3:I3"/>
+    <mergeCell ref="C4:I4"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C5:I5"/>
+    <mergeCell ref="C6:I6"/>
+    <mergeCell ref="C7:I7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/card disdoc.xlsx
+++ b/card disdoc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5a34dfa97c331738/Documents/ilja/Unity/ld60/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="96" documentId="8_{0C438EE4-F750-43B6-8F91-DB4328E051E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FCCEF6DF-AD37-4E9B-9F21-5377E52F86E6}"/>
+  <xr:revisionPtr revIDLastSave="109" documentId="8_{0C438EE4-F750-43B6-8F91-DB4328E051E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{671BC9A9-A417-4AB5-81A5-6BD6FFC24168}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{B625C734-B299-4013-86DD-D50F51382B50}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{B625C734-B299-4013-86DD-D50F51382B50}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="107">
   <si>
     <t>Hand (pts)</t>
   </si>
@@ -237,15 +237,9 @@
     <t>you can destroy (right click) 6 to gain additional reroll and 0.5 multiplier</t>
   </si>
   <si>
-    <t xml:space="preserve"> each 1 grants 10 bonus points</t>
-  </si>
-  <si>
     <t>full house grants bonus 100 points</t>
   </si>
   <si>
-    <t>four of the kind grants bonus 167 points</t>
-  </si>
-  <si>
     <t>five of a kind grants bonus 333 points</t>
   </si>
   <si>
@@ -261,13 +255,7 @@
     <t>4 4 4 grants bonus 100 points</t>
   </si>
   <si>
-    <t>2 2 grants bonus 0.25 multiplier</t>
-  </si>
-  <si>
     <t>3 3 grants bonus 67 points</t>
-  </si>
-  <si>
-    <t>3 4 grants bonus 0.25 multiplier</t>
   </si>
   <si>
     <t>1 1 1 multiplies combination's point count by 2</t>
@@ -585,6 +573,30 @@
 2 - Do you still love us?
 1- ...
 2 - If you do, please, come back home (end call)</t>
+  </si>
+  <si>
+    <t>you can create street with 1 gap (1 2 4 5 6)</t>
+  </si>
+  <si>
+    <t>big stragiht grants additional 200 points</t>
+  </si>
+  <si>
+    <t>2 2 grants bonus 0.5 multiplier</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> each 1 grants 15 bonus points</t>
+  </si>
+  <si>
+    <t>change</t>
+  </si>
+  <si>
+    <t>new</t>
+  </si>
+  <si>
+    <t>3 4 grants bonus 0.5 multiplier</t>
+  </si>
+  <si>
+    <t>1 1 1 1 grants additoinal 200 points</t>
   </si>
 </sst>
 </file>
@@ -1474,11 +1486,14 @@
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="N16" t="s">
+        <v>103</v>
+      </c>
       <c r="O16">
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>65</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.25">
@@ -1569,7 +1584,7 @@
         <v>6</v>
       </c>
       <c r="P21" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" spans="2:17" ht="30" x14ac:dyDescent="0.25">
@@ -1605,11 +1620,14 @@
       <c r="E23" s="2" t="s">
         <v>57</v>
       </c>
+      <c r="N23" t="s">
+        <v>103</v>
+      </c>
       <c r="O23">
         <v>8</v>
       </c>
       <c r="P23" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
     </row>
     <row r="24" spans="2:17" x14ac:dyDescent="0.25">
@@ -1629,7 +1647,7 @@
         <v>9</v>
       </c>
       <c r="P24" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25" spans="2:17" x14ac:dyDescent="0.25">
@@ -1637,7 +1655,7 @@
         <v>10</v>
       </c>
       <c r="P25" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" spans="2:17" x14ac:dyDescent="0.25">
@@ -1645,7 +1663,7 @@
         <v>11</v>
       </c>
       <c r="P26" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27" spans="2:17" x14ac:dyDescent="0.25">
@@ -1653,7 +1671,7 @@
         <v>12</v>
       </c>
       <c r="P27" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="28" spans="2:17" x14ac:dyDescent="0.25">
@@ -1661,7 +1679,7 @@
         <v>13</v>
       </c>
       <c r="P28" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29" spans="2:17" x14ac:dyDescent="0.25">
@@ -1681,11 +1699,14 @@
       </c>
     </row>
     <row r="31" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="N31" t="s">
+        <v>103</v>
+      </c>
       <c r="O31">
         <v>16</v>
       </c>
       <c r="P31" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
     </row>
     <row r="32" spans="2:17" x14ac:dyDescent="0.25">
@@ -1696,7 +1717,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="33" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="14:16" x14ac:dyDescent="0.25">
       <c r="O33">
         <v>18</v>
       </c>
@@ -1704,89 +1725,104 @@
         <v>41</v>
       </c>
     </row>
-    <row r="34" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="14:16" x14ac:dyDescent="0.25">
       <c r="O34">
         <v>19</v>
       </c>
       <c r="P34" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="35" spans="15:16" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="35" spans="14:16" x14ac:dyDescent="0.25">
+      <c r="N35" t="s">
+        <v>103</v>
+      </c>
       <c r="O35">
         <v>20</v>
       </c>
       <c r="P35" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="36" spans="15:16" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="36" spans="14:16" x14ac:dyDescent="0.25">
       <c r="O36">
         <v>21</v>
       </c>
       <c r="P36" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="37" spans="15:16" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="37" spans="14:16" x14ac:dyDescent="0.25">
       <c r="O37">
         <v>22</v>
       </c>
       <c r="P37" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="38" spans="15:16" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="38" spans="14:16" x14ac:dyDescent="0.25">
+      <c r="N38" t="s">
+        <v>104</v>
+      </c>
       <c r="O38">
         <v>23</v>
       </c>
-    </row>
-    <row r="39" spans="15:16" x14ac:dyDescent="0.25">
+      <c r="P38" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="39" spans="14:16" x14ac:dyDescent="0.25">
+      <c r="N39" t="s">
+        <v>104</v>
+      </c>
       <c r="O39">
         <v>24</v>
       </c>
-    </row>
-    <row r="40" spans="15:16" x14ac:dyDescent="0.25">
+      <c r="P39" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="14:16" x14ac:dyDescent="0.25">
       <c r="O40">
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="14:16" x14ac:dyDescent="0.25">
       <c r="O41">
         <v>26</v>
       </c>
     </row>
-    <row r="42" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="42" spans="14:16" x14ac:dyDescent="0.25">
       <c r="O42">
         <v>27</v>
       </c>
     </row>
-    <row r="43" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="14:16" x14ac:dyDescent="0.25">
       <c r="O43">
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="14:16" x14ac:dyDescent="0.25">
       <c r="O44">
         <v>29</v>
       </c>
     </row>
-    <row r="45" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="14:16" x14ac:dyDescent="0.25">
       <c r="O45">
         <v>30</v>
       </c>
     </row>
-    <row r="46" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="14:16" x14ac:dyDescent="0.25">
       <c r="O46">
         <v>31</v>
       </c>
     </row>
-    <row r="47" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="47" spans="14:16" x14ac:dyDescent="0.25">
       <c r="O47">
         <v>32</v>
       </c>
     </row>
-    <row r="48" spans="15:16" x14ac:dyDescent="0.25">
+    <row r="48" spans="14:16" x14ac:dyDescent="0.25">
       <c r="O48">
         <v>33</v>
       </c>
@@ -1834,10 +1870,10 @@
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
       <c r="B1" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>78</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>82</v>
       </c>
       <c r="D1" s="7"/>
       <c r="E1" s="7"/>
@@ -1848,13 +1884,13 @@
     </row>
     <row r="2" spans="1:12" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>83</v>
-      </c>
       <c r="C2" s="9" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D2" s="8"/>
       <c r="E2" s="8"/>
@@ -1863,16 +1899,16 @@
       <c r="H2" s="8"/>
       <c r="I2" s="8"/>
       <c r="L2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B3" s="7"/>
       <c r="C3" s="9" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
@@ -1881,16 +1917,16 @@
       <c r="H3" s="8"/>
       <c r="I3" s="8"/>
       <c r="L3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="9" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
@@ -1899,18 +1935,18 @@
       <c r="H4" s="8"/>
       <c r="I4" s="8"/>
       <c r="L4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
@@ -1919,16 +1955,16 @@
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
       <c r="L5" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="9" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
@@ -1939,11 +1975,11 @@
     </row>
     <row r="7" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="9" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
@@ -1954,13 +1990,13 @@
     </row>
     <row r="8" spans="1:12" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
@@ -1971,11 +2007,11 @@
     </row>
     <row r="9" spans="1:12" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="9" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
@@ -1986,11 +2022,11 @@
     </row>
     <row r="10" spans="1:12" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="9" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
@@ -2001,13 +2037,13 @@
     </row>
     <row r="11" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B11" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11" s="9" t="s">
         <v>95</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>99</v>
       </c>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
@@ -2018,11 +2054,11 @@
     </row>
     <row r="12" spans="1:12" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="9" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
@@ -2033,11 +2069,11 @@
     </row>
     <row r="13" spans="1:12" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="9" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>

--- a/card disdoc.xlsx
+++ b/card disdoc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5a34dfa97c331738/Documents/ilja/Unity/ld60/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="109" documentId="8_{0C438EE4-F750-43B6-8F91-DB4328E051E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{671BC9A9-A417-4AB5-81A5-6BD6FFC24168}"/>
+  <xr:revisionPtr revIDLastSave="144" documentId="8_{0C438EE4-F750-43B6-8F91-DB4328E051E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10702871-4A83-4D80-B4FF-851413DDB58A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{B625C734-B299-4013-86DD-D50F51382B50}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{B625C734-B299-4013-86DD-D50F51382B50}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="122">
   <si>
     <t>Hand (pts)</t>
   </si>
@@ -597,6 +597,74 @@
   </si>
   <si>
     <t>1 1 1 1 grants additoinal 200 points</t>
+  </si>
+  <si>
+    <t>interactable:</t>
+  </si>
+  <si>
+    <t>vynil player:</t>
+  </si>
+  <si>
+    <t>Every time i listen to this song, i feel like I am rotting alive
+But this pain is so beautiful and pleasant
+Perfect song for my funerals</t>
+  </si>
+  <si>
+    <t>It is my favorite part
+Silence moment before storm
+It sounds very sad
+It hopeful at the same time
+I used to call this feeling: melancholy
+Until i found out it has different meaning</t>
+  </si>
+  <si>
+    <t>its the end</t>
+  </si>
+  <si>
+    <t>Listening to this part, i feel only hatred
+out of onwhere 
+I dont know why</t>
+  </si>
+  <si>
+    <t>Character</t>
+  </si>
+  <si>
+    <t>First</t>
+  </si>
+  <si>
+    <t>after mom</t>
+  </si>
+  <si>
+    <t>after friend</t>
+  </si>
+  <si>
+    <t>after gf</t>
+  </si>
+  <si>
+    <t>I love my mother more than anything else in this world
+What i have become
+if she lost her hope...
+if Even she...
+How i caould...
+if she does, I surely do not deserve to live anymore</t>
+  </si>
+  <si>
+    <t>Maybe i am doing wrong.
+I've already made up my mind in any case.
+What people usually do in such moments?
+If think i need to call and say goodbye to some people</t>
+  </si>
+  <si>
+    <t>what is he not care about me at all this whole time?
+He is the person who new about me more than anyone else
+if even he didnt care about me, there nobody who does
+And i can pass away peacefully</t>
+  </si>
+  <si>
+    <t>We were perfect
+It sounds silly, but I think it really was
+Everybody think, it really was...
+I am jsut a selffish bitch</t>
   </si>
 </sst>
 </file>
@@ -640,7 +708,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -668,6 +736,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1864,7 +1936,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10006A7A-F87C-4A54-AC2B-0B8DC3F5EB25}">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:R24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -2081,6 +2153,73 @@
       <c r="G13" s="8"/>
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
+    </row>
+    <row r="18" spans="13:18" x14ac:dyDescent="0.25">
+      <c r="M18" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="19" spans="13:18" x14ac:dyDescent="0.25">
+      <c r="O19" s="10">
+        <v>0</v>
+      </c>
+      <c r="P19" s="10">
+        <v>0.25</v>
+      </c>
+      <c r="Q19" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="R19" s="10">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="20" spans="13:18" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M20" t="s">
+        <v>108</v>
+      </c>
+      <c r="O20" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="P20" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q20" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="R20" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="23" spans="13:18" x14ac:dyDescent="0.25">
+      <c r="N23" t="s">
+        <v>114</v>
+      </c>
+      <c r="O23" t="s">
+        <v>115</v>
+      </c>
+      <c r="P23" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="24" spans="13:18" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M24" t="s">
+        <v>113</v>
+      </c>
+      <c r="N24" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="O24" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="P24" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q24" s="11" t="s">
+        <v>121</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="17">

--- a/card disdoc.xlsx
+++ b/card disdoc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5a34dfa97c331738/Documents/ilja/Unity/ld60/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="144" documentId="8_{0C438EE4-F750-43B6-8F91-DB4328E051E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10702871-4A83-4D80-B4FF-851413DDB58A}"/>
+  <xr:revisionPtr revIDLastSave="168" documentId="8_{0C438EE4-F750-43B6-8F91-DB4328E051E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10D7CE17-7921-4F70-B268-D673E92ABE74}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{B625C734-B299-4013-86DD-D50F51382B50}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{B625C734-B299-4013-86DD-D50F51382B50}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="137">
   <si>
     <t>Hand (pts)</t>
   </si>
@@ -665,6 +665,51 @@
 It sounds silly, but I think it really was
 Everybody think, it really was...
 I am jsut a selffish bitch</t>
+  </si>
+  <si>
+    <t>Dices:</t>
+  </si>
+  <si>
+    <t>Color</t>
+  </si>
+  <si>
+    <t>Blue</t>
+  </si>
+  <si>
+    <t>pink</t>
+  </si>
+  <si>
+    <t>effect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Always odd </t>
+  </si>
+  <si>
+    <t>Yellow</t>
+  </si>
+  <si>
+    <t>always even</t>
+  </si>
+  <si>
+    <t>Green</t>
+  </si>
+  <si>
+    <t>cyan</t>
+  </si>
+  <si>
+    <t>red</t>
+  </si>
+  <si>
+    <t>u can always change this die value to 1</t>
+  </si>
+  <si>
+    <t>cannot be 1 2 or 3</t>
+  </si>
+  <si>
+    <t>change its value to most common value of all dices</t>
+  </si>
+  <si>
+    <t>value always differs from all dices</t>
   </si>
 </sst>
 </file>
@@ -708,7 +753,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -724,6 +769,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1763,6 +1811,9 @@
       </c>
     </row>
     <row r="30" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="C30" t="s">
+        <v>122</v>
+      </c>
       <c r="O30">
         <v>15</v>
       </c>
@@ -1771,6 +1822,16 @@
       </c>
     </row>
     <row r="31" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="C31" t="s">
+        <v>123</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
       <c r="N31" t="s">
         <v>103</v>
       </c>
@@ -1782,6 +1843,16 @@
       </c>
     </row>
     <row r="32" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="C32" t="s">
+        <v>124</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
       <c r="O32">
         <v>17</v>
       </c>
@@ -1789,7 +1860,17 @@
         <v>61</v>
       </c>
     </row>
-    <row r="33" spans="14:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="C33" t="s">
+        <v>128</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
       <c r="O33">
         <v>18</v>
       </c>
@@ -1797,7 +1878,17 @@
         <v>41</v>
       </c>
     </row>
-    <row r="34" spans="14:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="C34" t="s">
+        <v>125</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
       <c r="O34">
         <v>19</v>
       </c>
@@ -1805,7 +1896,17 @@
         <v>65</v>
       </c>
     </row>
-    <row r="35" spans="14:16" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="C35" t="s">
+        <v>130</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
       <c r="N35" t="s">
         <v>103</v>
       </c>
@@ -1816,7 +1917,17 @@
         <v>106</v>
       </c>
     </row>
-    <row r="36" spans="14:16" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="C36" t="s">
+        <v>131</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
       <c r="O36">
         <v>21</v>
       </c>
@@ -1824,7 +1935,17 @@
         <v>66</v>
       </c>
     </row>
-    <row r="37" spans="14:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="C37" t="s">
+        <v>132</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
       <c r="O37">
         <v>22</v>
       </c>
@@ -1832,7 +1953,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="38" spans="14:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:16" x14ac:dyDescent="0.25">
       <c r="N38" t="s">
         <v>104</v>
       </c>
@@ -1843,7 +1964,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="39" spans="14:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:16" x14ac:dyDescent="0.25">
       <c r="N39" t="s">
         <v>104</v>
       </c>
@@ -1854,47 +1975,47 @@
         <v>100</v>
       </c>
     </row>
-    <row r="40" spans="14:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:16" x14ac:dyDescent="0.25">
       <c r="O40">
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="14:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:16" x14ac:dyDescent="0.25">
       <c r="O41">
         <v>26</v>
       </c>
     </row>
-    <row r="42" spans="14:16" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:16" x14ac:dyDescent="0.25">
       <c r="O42">
         <v>27</v>
       </c>
     </row>
-    <row r="43" spans="14:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:16" x14ac:dyDescent="0.25">
       <c r="O43">
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="14:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:16" x14ac:dyDescent="0.25">
       <c r="O44">
         <v>29</v>
       </c>
     </row>
-    <row r="45" spans="14:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:16" x14ac:dyDescent="0.25">
       <c r="O45">
         <v>30</v>
       </c>
     </row>
-    <row r="46" spans="14:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:16" x14ac:dyDescent="0.25">
       <c r="O46">
         <v>31</v>
       </c>
     </row>
-    <row r="47" spans="14:16" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:16" x14ac:dyDescent="0.25">
       <c r="O47">
         <v>32</v>
       </c>
     </row>
-    <row r="48" spans="14:16" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:16" x14ac:dyDescent="0.25">
       <c r="O48">
         <v>33</v>
       </c>
@@ -1930,6 +2051,15 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="D37:H37"/>
+    <mergeCell ref="D31:H31"/>
+    <mergeCell ref="D32:H32"/>
+    <mergeCell ref="D33:H33"/>
+    <mergeCell ref="D34:H34"/>
+    <mergeCell ref="D35:H35"/>
+    <mergeCell ref="D36:H36"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1940,219 +2070,219 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="6"/>
-      <c r="B1" s="6" t="s">
+      <c r="A1" s="7"/>
+      <c r="B1" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
     </row>
     <row r="2" spans="1:12" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
       <c r="L2" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="9" t="s">
+      <c r="B3" s="8"/>
+      <c r="C3" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
       <c r="L3" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="9" t="s">
+      <c r="B4" s="8"/>
+      <c r="C4" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
       <c r="L4" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
       <c r="L5" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="9" t="s">
+      <c r="B6" s="8"/>
+      <c r="C6" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
     </row>
     <row r="7" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="9" t="s">
+      <c r="B7" s="8"/>
+      <c r="C7" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
     </row>
     <row r="8" spans="1:12" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
     </row>
     <row r="9" spans="1:12" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="9" t="s">
+      <c r="B9" s="8"/>
+      <c r="C9" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
     </row>
     <row r="10" spans="1:12" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="9" t="s">
+      <c r="B10" s="8"/>
+      <c r="C10" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
     </row>
     <row r="11" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
     </row>
     <row r="12" spans="1:12" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="9" t="s">
+      <c r="B12" s="8"/>
+      <c r="C12" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
     </row>
     <row r="13" spans="1:12" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="9" t="s">
+      <c r="B13" s="8"/>
+      <c r="C13" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
     </row>
     <row r="18" spans="13:18" x14ac:dyDescent="0.25">
       <c r="M18" t="s">
@@ -2160,16 +2290,16 @@
       </c>
     </row>
     <row r="19" spans="13:18" x14ac:dyDescent="0.25">
-      <c r="O19" s="10">
+      <c r="O19" s="11">
         <v>0</v>
       </c>
-      <c r="P19" s="10">
+      <c r="P19" s="11">
         <v>0.25</v>
       </c>
-      <c r="Q19" s="10">
+      <c r="Q19" s="11">
         <v>0.5</v>
       </c>
-      <c r="R19" s="10">
+      <c r="R19" s="11">
         <v>0.75</v>
       </c>
     </row>
@@ -2177,13 +2307,13 @@
       <c r="M20" t="s">
         <v>108</v>
       </c>
-      <c r="O20" s="11" t="s">
+      <c r="O20" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="P20" s="11" t="s">
+      <c r="P20" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="Q20" s="11" t="s">
+      <c r="Q20" s="12" t="s">
         <v>110</v>
       </c>
       <c r="R20" t="s">
@@ -2208,16 +2338,16 @@
       <c r="M24" t="s">
         <v>113</v>
       </c>
-      <c r="N24" s="11" t="s">
+      <c r="N24" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="O24" s="11" t="s">
+      <c r="O24" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="P24" s="11" t="s">
+      <c r="P24" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="Q24" s="11" t="s">
+      <c r="Q24" s="12" t="s">
         <v>121</v>
       </c>
     </row>

--- a/card disdoc.xlsx
+++ b/card disdoc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5a34dfa97c331738/Documents/ilja/Unity/ld60/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="168" documentId="8_{0C438EE4-F750-43B6-8F91-DB4328E051E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10D7CE17-7921-4F70-B268-D673E92ABE74}"/>
+  <xr:revisionPtr revIDLastSave="176" documentId="8_{0C438EE4-F750-43B6-8F91-DB4328E051E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0213386-FDA6-4025-BA93-E3EED77E9006}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{B625C734-B299-4013-86DD-D50F51382B50}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="136">
   <si>
     <t>Hand (pts)</t>
   </si>
@@ -163,9 +163,6 @@
   </si>
   <si>
     <t>1 1 grants 52 bonus points</t>
-  </si>
-  <si>
-    <t>result multiplies by 2 if all dices are even</t>
   </si>
   <si>
     <t>44 / 44</t>
@@ -590,9 +587,6 @@
     <t>change</t>
   </si>
   <si>
-    <t>new</t>
-  </si>
-  <si>
     <t>3 4 grants bonus 0.5 multiplier</t>
   </si>
   <si>
@@ -710,6 +704,9 @@
   </si>
   <si>
     <t>value always differs from all dices</t>
+  </si>
+  <si>
+    <t>grants 2 multiplier, if there are more even dices then odd</t>
   </si>
 </sst>
 </file>
@@ -1607,13 +1604,13 @@
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="N16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O16">
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.25">
@@ -1649,19 +1646,19 @@
         <v>0</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="O19">
         <v>4</v>
       </c>
       <c r="P19" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="Q19" t="s">
         <v>36</v>
@@ -1672,13 +1669,13 @@
         <v>1</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="E20" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="O20">
         <v>5</v>
@@ -1692,33 +1689,33 @@
         <v>2</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="E21" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="O21">
         <v>6</v>
       </c>
       <c r="P21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22" spans="2:17" ht="30" x14ac:dyDescent="0.25">
       <c r="B22" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="D22" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="E22" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="O22">
         <v>7</v>
@@ -1732,22 +1729,19 @@
         <v>4</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="E23" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="N23" t="s">
-        <v>103</v>
       </c>
       <c r="O23">
         <v>8</v>
       </c>
       <c r="P23" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="2:17" x14ac:dyDescent="0.25">
@@ -1755,19 +1749,19 @@
         <v>5</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="E24" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="O24">
         <v>9</v>
       </c>
       <c r="P24" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25" spans="2:17" x14ac:dyDescent="0.25">
@@ -1775,7 +1769,7 @@
         <v>10</v>
       </c>
       <c r="P25" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26" spans="2:17" x14ac:dyDescent="0.25">
@@ -1783,7 +1777,7 @@
         <v>11</v>
       </c>
       <c r="P26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="27" spans="2:17" x14ac:dyDescent="0.25">
@@ -1791,7 +1785,7 @@
         <v>12</v>
       </c>
       <c r="P27" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28" spans="2:17" x14ac:dyDescent="0.25">
@@ -1799,7 +1793,7 @@
         <v>13</v>
       </c>
       <c r="P28" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29" spans="2:17" x14ac:dyDescent="0.25">
@@ -1807,47 +1801,44 @@
         <v>14</v>
       </c>
       <c r="P29" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="30" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C30" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="O30">
         <v>15</v>
       </c>
       <c r="P30" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="31" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C31" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
       <c r="H31" s="6"/>
-      <c r="N31" t="s">
-        <v>103</v>
-      </c>
       <c r="O31">
         <v>16</v>
       </c>
       <c r="P31" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="32" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C32" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
@@ -1857,33 +1848,36 @@
         <v>17</v>
       </c>
       <c r="P32" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="33" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C33" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
       <c r="H33" s="6"/>
+      <c r="N33" t="s">
+        <v>102</v>
+      </c>
       <c r="O33">
         <v>18</v>
       </c>
       <c r="P33" t="s">
-        <v>41</v>
+        <v>135</v>
       </c>
     </row>
     <row r="34" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C34" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
@@ -1893,36 +1887,33 @@
         <v>19</v>
       </c>
       <c r="P34" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="35" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C35" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
       <c r="G35" s="6"/>
       <c r="H35" s="6"/>
-      <c r="N35" t="s">
-        <v>103</v>
-      </c>
       <c r="O35">
         <v>20</v>
       </c>
       <c r="P35" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="36" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C36" t="s">
+        <v>129</v>
+      </c>
+      <c r="D36" s="6" t="s">
         <v>131</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>133</v>
       </c>
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
@@ -1932,15 +1923,15 @@
         <v>21</v>
       </c>
       <c r="P36" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="37" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C37" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
@@ -1950,29 +1941,23 @@
         <v>22</v>
       </c>
       <c r="P37" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="38" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="N38" t="s">
-        <v>104</v>
-      </c>
       <c r="O38">
         <v>23</v>
       </c>
       <c r="P38" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="39" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="N39" t="s">
-        <v>104</v>
-      </c>
       <c r="O39">
         <v>24</v>
       </c>
       <c r="P39" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="40" spans="3:16" x14ac:dyDescent="0.25">
@@ -2072,10 +2057,10 @@
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D1" s="8"/>
       <c r="E1" s="8"/>
@@ -2086,13 +2071,13 @@
     </row>
     <row r="2" spans="1:12" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
@@ -2101,16 +2086,16 @@
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
       <c r="L2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -2119,16 +2104,16 @@
       <c r="H3" s="9"/>
       <c r="I3" s="9"/>
       <c r="L3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -2137,18 +2122,18 @@
       <c r="H4" s="9"/>
       <c r="I4" s="9"/>
       <c r="L4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
@@ -2157,16 +2142,16 @@
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
       <c r="L5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
@@ -2177,11 +2162,11 @@
     </row>
     <row r="7" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
@@ -2192,13 +2177,13 @@
     </row>
     <row r="8" spans="1:12" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
@@ -2209,11 +2194,11 @@
     </row>
     <row r="9" spans="1:12" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
@@ -2224,11 +2209,11 @@
     </row>
     <row r="10" spans="1:12" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B10" s="8"/>
       <c r="C10" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
@@ -2239,13 +2224,13 @@
     </row>
     <row r="11" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
@@ -2256,11 +2241,11 @@
     </row>
     <row r="12" spans="1:12" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
@@ -2271,11 +2256,11 @@
     </row>
     <row r="13" spans="1:12" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
@@ -2286,7 +2271,7 @@
     </row>
     <row r="18" spans="13:18" x14ac:dyDescent="0.25">
       <c r="M18" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" spans="13:18" x14ac:dyDescent="0.25">
@@ -2305,50 +2290,50 @@
     </row>
     <row r="20" spans="13:18" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M20" t="s">
+        <v>106</v>
+      </c>
+      <c r="O20" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="P20" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q20" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="O20" s="12" t="s">
+      <c r="R20" t="s">
         <v>109</v>
-      </c>
-      <c r="P20" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="Q20" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="R20" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="23" spans="13:18" x14ac:dyDescent="0.25">
       <c r="N23" t="s">
+        <v>112</v>
+      </c>
+      <c r="O23" t="s">
+        <v>113</v>
+      </c>
+      <c r="P23" t="s">
         <v>114</v>
       </c>
-      <c r="O23" t="s">
+      <c r="Q23" t="s">
         <v>115</v>
-      </c>
-      <c r="P23" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="24" spans="13:18" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M24" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="N24" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="O24" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="P24" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q24" s="12" t="s">
         <v>119</v>
-      </c>
-      <c r="O24" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="P24" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q24" s="12" t="s">
-        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/card disdoc.xlsx
+++ b/card disdoc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5a34dfa97c331738/Documents/ilja/Unity/ld60/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="176" documentId="8_{0C438EE4-F750-43B6-8F91-DB4328E051E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0213386-FDA6-4025-BA93-E3EED77E9006}"/>
+  <xr:revisionPtr revIDLastSave="179" documentId="8_{0C438EE4-F750-43B6-8F91-DB4328E051E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB656DCB-ECA5-4B2A-9A5D-F070D9A56C5A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{B625C734-B299-4013-86DD-D50F51382B50}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="136">
   <si>
     <t>Hand (pts)</t>
   </si>
@@ -572,9 +572,6 @@
 2 - If you do, please, come back home (end call)</t>
   </si>
   <si>
-    <t>you can create street with 1 gap (1 2 4 5 6)</t>
-  </si>
-  <si>
     <t>big stragiht grants additional 200 points</t>
   </si>
   <si>
@@ -707,6 +704,9 @@
   </si>
   <si>
     <t>grants 2 multiplier, if there are more even dices then odd</t>
+  </si>
+  <si>
+    <t>stragiht grants additional 100 points</t>
   </si>
 </sst>
 </file>
@@ -1604,13 +1604,13 @@
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="N16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O16">
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.25">
@@ -1741,7 +1741,7 @@
         <v>8</v>
       </c>
       <c r="P23" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="2:17" x14ac:dyDescent="0.25">
@@ -1806,7 +1806,7 @@
     </row>
     <row r="30" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C30" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O30">
         <v>15</v>
@@ -1817,10 +1817,10 @@
     </row>
     <row r="31" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C31" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
@@ -1830,15 +1830,15 @@
         <v>16</v>
       </c>
       <c r="P31" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="32" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C32" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
@@ -1853,31 +1853,31 @@
     </row>
     <row r="33" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C33" t="s">
+        <v>125</v>
+      </c>
+      <c r="D33" s="6" t="s">
         <v>126</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>127</v>
       </c>
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
       <c r="H33" s="6"/>
       <c r="N33" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O33">
         <v>18</v>
       </c>
       <c r="P33" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="34" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C34" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
@@ -1892,10 +1892,10 @@
     </row>
     <row r="35" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C35" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
@@ -1905,15 +1905,15 @@
         <v>20</v>
       </c>
       <c r="P35" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="36" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C36" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
@@ -1928,10 +1928,10 @@
     </row>
     <row r="37" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C37" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
@@ -1945,11 +1945,14 @@
       </c>
     </row>
     <row r="38" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="N38" t="s">
+        <v>101</v>
+      </c>
       <c r="O38">
         <v>23</v>
       </c>
       <c r="P38" t="s">
-        <v>98</v>
+        <v>135</v>
       </c>
     </row>
     <row r="39" spans="3:16" x14ac:dyDescent="0.25">
@@ -1957,7 +1960,7 @@
         <v>24</v>
       </c>
       <c r="P39" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="40" spans="3:16" x14ac:dyDescent="0.25">
@@ -2271,7 +2274,7 @@
     </row>
     <row r="18" spans="13:18" x14ac:dyDescent="0.25">
       <c r="M18" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" spans="13:18" x14ac:dyDescent="0.25">
@@ -2290,50 +2293,50 @@
     </row>
     <row r="20" spans="13:18" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M20" t="s">
+        <v>105</v>
+      </c>
+      <c r="O20" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="O20" s="12" t="s">
+      <c r="P20" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q20" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="P20" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q20" s="12" t="s">
+      <c r="R20" t="s">
         <v>108</v>
-      </c>
-      <c r="R20" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="23" spans="13:18" x14ac:dyDescent="0.25">
       <c r="N23" t="s">
+        <v>111</v>
+      </c>
+      <c r="O23" t="s">
         <v>112</v>
       </c>
-      <c r="O23" t="s">
+      <c r="P23" t="s">
         <v>113</v>
       </c>
-      <c r="P23" t="s">
+      <c r="Q23" t="s">
         <v>114</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="24" spans="13:18" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M24" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="N24" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="O24" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="P24" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="O24" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="P24" s="12" t="s">
+      <c r="Q24" s="12" t="s">
         <v>118</v>
-      </c>
-      <c r="Q24" s="12" t="s">
-        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/card disdoc.xlsx
+++ b/card disdoc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5a34dfa97c331738/Documents/ilja/Unity/ld60/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="179" documentId="8_{0C438EE4-F750-43B6-8F91-DB4328E051E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB656DCB-ECA5-4B2A-9A5D-F070D9A56C5A}"/>
+  <xr:revisionPtr revIDLastSave="203" documentId="8_{0C438EE4-F750-43B6-8F91-DB4328E051E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C850EE7-8117-460B-808E-BE590451C44C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{B625C734-B299-4013-86DD-D50F51382B50}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="136">
   <si>
     <t>Hand (pts)</t>
   </si>
@@ -225,9 +225,6 @@
     <t>odd dices grant bonus 0.2 multiplier</t>
   </si>
   <si>
-    <t>1 6 grants 1.5 multiplier</t>
-  </si>
-  <si>
     <t>2 5 grants bonus 67 points</t>
   </si>
   <si>
@@ -240,9 +237,6 @@
     <t>five of a kind grants bonus 333 points</t>
   </si>
   <si>
-    <t>street multiplies grants 2 multiplier</t>
-  </si>
-  <si>
     <t>6 6 6 grants bonus 100 points</t>
   </si>
   <si>
@@ -253,9 +247,6 @@
   </si>
   <si>
     <t>3 3 grants bonus 67 points</t>
-  </si>
-  <si>
-    <t>1 1 1 multiplies combination's point count by 2</t>
   </si>
   <si>
     <t>1 2 3 grants 50 points and 1 additional reroll next round</t>
@@ -578,9 +569,6 @@
     <t>2 2 grants bonus 0.5 multiplier</t>
   </si>
   <si>
-    <t xml:space="preserve"> each 1 grants 15 bonus points</t>
-  </si>
-  <si>
     <t>change</t>
   </si>
   <si>
@@ -707,6 +695,18 @@
   </si>
   <si>
     <t>stragiht grants additional 100 points</t>
+  </si>
+  <si>
+    <t>1 6 grants 0.5 multiplier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 1 1 grants 1.11 multiplier </t>
+  </si>
+  <si>
+    <t>straight grants 3.33 multiplier</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> each 4 grants 15 bonus points</t>
   </si>
 </sst>
 </file>
@@ -1604,13 +1604,13 @@
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="N16" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="O16">
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>100</v>
+        <v>135</v>
       </c>
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.25">
@@ -1658,7 +1658,7 @@
         <v>4</v>
       </c>
       <c r="P19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q19" t="s">
         <v>36</v>
@@ -1697,11 +1697,14 @@
       <c r="E21" s="2" t="s">
         <v>49</v>
       </c>
+      <c r="N21" t="s">
+        <v>97</v>
+      </c>
       <c r="O21">
         <v>6</v>
       </c>
       <c r="P21" t="s">
-        <v>71</v>
+        <v>133</v>
       </c>
     </row>
     <row r="22" spans="2:17" ht="30" x14ac:dyDescent="0.25">
@@ -1741,7 +1744,7 @@
         <v>8</v>
       </c>
       <c r="P23" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="24" spans="2:17" x14ac:dyDescent="0.25">
@@ -1761,15 +1764,18 @@
         <v>9</v>
       </c>
       <c r="P24" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="N25" t="s">
+        <v>97</v>
+      </c>
       <c r="O25">
         <v>10</v>
       </c>
       <c r="P25" t="s">
-        <v>66</v>
+        <v>134</v>
       </c>
     </row>
     <row r="26" spans="2:17" x14ac:dyDescent="0.25">
@@ -1777,7 +1783,7 @@
         <v>11</v>
       </c>
       <c r="P26" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="27" spans="2:17" x14ac:dyDescent="0.25">
@@ -1785,7 +1791,7 @@
         <v>12</v>
       </c>
       <c r="P27" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="28" spans="2:17" x14ac:dyDescent="0.25">
@@ -1793,34 +1799,37 @@
         <v>13</v>
       </c>
       <c r="P28" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="N29" t="s">
+        <v>97</v>
+      </c>
       <c r="O29">
         <v>14</v>
       </c>
       <c r="P29" t="s">
-        <v>61</v>
+        <v>132</v>
       </c>
     </row>
     <row r="30" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C30" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="O30">
         <v>15</v>
       </c>
       <c r="P30" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="31" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C31" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
@@ -1830,15 +1839,15 @@
         <v>16</v>
       </c>
       <c r="P31" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="32" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C32" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
@@ -1853,31 +1862,31 @@
     </row>
     <row r="33" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C33" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
       <c r="H33" s="6"/>
       <c r="N33" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="O33">
         <v>18</v>
       </c>
       <c r="P33" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="34" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C34" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
@@ -1887,15 +1896,15 @@
         <v>19</v>
       </c>
       <c r="P34" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="35" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C35" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
@@ -1905,15 +1914,15 @@
         <v>20</v>
       </c>
       <c r="P35" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="36" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C36" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
@@ -1923,15 +1932,15 @@
         <v>21</v>
       </c>
       <c r="P36" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="37" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C37" t="s">
+        <v>125</v>
+      </c>
+      <c r="D37" s="6" t="s">
         <v>129</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>133</v>
       </c>
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
@@ -1941,18 +1950,18 @@
         <v>22</v>
       </c>
       <c r="P37" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="38" spans="3:16" x14ac:dyDescent="0.25">
       <c r="N38" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="O38">
         <v>23</v>
       </c>
       <c r="P38" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="39" spans="3:16" x14ac:dyDescent="0.25">
@@ -1960,7 +1969,7 @@
         <v>24</v>
       </c>
       <c r="P39" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="40" spans="3:16" x14ac:dyDescent="0.25">
@@ -2060,10 +2069,10 @@
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D1" s="8"/>
       <c r="E1" s="8"/>
@@ -2074,13 +2083,13 @@
     </row>
     <row r="2" spans="1:12" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
@@ -2089,16 +2098,16 @@
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
       <c r="L2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="10" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -2107,16 +2116,16 @@
       <c r="H3" s="9"/>
       <c r="I3" s="9"/>
       <c r="L3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="10" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -2125,18 +2134,18 @@
       <c r="H4" s="9"/>
       <c r="I4" s="9"/>
       <c r="L4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
@@ -2145,16 +2154,16 @@
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
       <c r="L5" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="10" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
@@ -2165,11 +2174,11 @@
     </row>
     <row r="7" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
@@ -2180,13 +2189,13 @@
     </row>
     <row r="8" spans="1:12" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
@@ -2197,11 +2206,11 @@
     </row>
     <row r="9" spans="1:12" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="10" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
@@ -2212,11 +2221,11 @@
     </row>
     <row r="10" spans="1:12" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B10" s="8"/>
       <c r="C10" s="10" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
@@ -2227,13 +2236,13 @@
     </row>
     <row r="11" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
@@ -2244,11 +2253,11 @@
     </row>
     <row r="12" spans="1:12" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="10" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
@@ -2259,11 +2268,11 @@
     </row>
     <row r="13" spans="1:12" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="10" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
@@ -2274,7 +2283,7 @@
     </row>
     <row r="18" spans="13:18" x14ac:dyDescent="0.25">
       <c r="M18" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="13:18" x14ac:dyDescent="0.25">
@@ -2293,50 +2302,50 @@
     </row>
     <row r="20" spans="13:18" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M20" t="s">
+        <v>101</v>
+      </c>
+      <c r="O20" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="P20" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="O20" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="P20" s="12" t="s">
-        <v>109</v>
-      </c>
       <c r="Q20" s="12" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="R20" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23" spans="13:18" x14ac:dyDescent="0.25">
       <c r="N23" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="O23" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="P23" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="Q23" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="24" spans="13:18" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M24" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="N24" s="12" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="O24" s="12" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="P24" s="12" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Q24" s="12" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/card disdoc.xlsx
+++ b/card disdoc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5a34dfa97c331738/Documents/ilja/Unity/ld60/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="203" documentId="8_{0C438EE4-F750-43B6-8F91-DB4328E051E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C850EE7-8117-460B-808E-BE590451C44C}"/>
+  <xr:revisionPtr revIDLastSave="223" documentId="8_{0C438EE4-F750-43B6-8F91-DB4328E051E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F086FD1-4C0D-4E33-8082-7A3DE68E6FD3}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{B625C734-B299-4013-86DD-D50F51382B50}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="136">
   <si>
     <t>Hand (pts)</t>
   </si>
@@ -225,9 +225,6 @@
     <t>odd dices grant bonus 0.2 multiplier</t>
   </si>
   <si>
-    <t>2 5 grants bonus 67 points</t>
-  </si>
-  <si>
     <t>you can destroy (right click) 6 to gain additional reroll and 0.5 multiplier</t>
   </si>
   <si>
@@ -244,9 +241,6 @@
   </si>
   <si>
     <t>4 4 4 grants bonus 100 points</t>
-  </si>
-  <si>
-    <t>3 3 grants bonus 67 points</t>
   </si>
   <si>
     <t>1 2 3 grants 50 points and 1 additional reroll next round</t>
@@ -566,13 +560,7 @@
     <t>big stragiht grants additional 200 points</t>
   </si>
   <si>
-    <t>2 2 grants bonus 0.5 multiplier</t>
-  </si>
-  <si>
     <t>change</t>
-  </si>
-  <si>
-    <t>3 4 grants bonus 0.5 multiplier</t>
   </si>
   <si>
     <t>1 1 1 1 grants additoinal 200 points</t>
@@ -703,10 +691,22 @@
     <t xml:space="preserve">1 1 1 grants 1.11 multiplier </t>
   </si>
   <si>
-    <t>straight grants 3.33 multiplier</t>
-  </si>
-  <si>
     <t xml:space="preserve"> each 4 grants 15 bonus points</t>
+  </si>
+  <si>
+    <t>each 2 2 grants bonus 0.5 multiplier</t>
+  </si>
+  <si>
+    <t>each 3 3 grants bonus 67 points</t>
+  </si>
+  <si>
+    <t>each 2 5 grants bonus 67 points</t>
+  </si>
+  <si>
+    <t>each 3 4 grants bonus 0.5 multiplier</t>
+  </si>
+  <si>
+    <t>straight grants 1 multiplier</t>
   </si>
 </sst>
 </file>
@@ -1603,14 +1603,11 @@
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="N16" t="s">
-        <v>97</v>
-      </c>
       <c r="O16">
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.25">
@@ -1658,7 +1655,7 @@
         <v>4</v>
       </c>
       <c r="P19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q19" t="s">
         <v>36</v>
@@ -1697,14 +1694,11 @@
       <c r="E21" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="N21" t="s">
-        <v>97</v>
-      </c>
       <c r="O21">
         <v>6</v>
       </c>
       <c r="P21" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="22" spans="2:17" ht="30" x14ac:dyDescent="0.25">
@@ -1744,7 +1738,7 @@
         <v>8</v>
       </c>
       <c r="P23" t="s">
-        <v>96</v>
+        <v>131</v>
       </c>
     </row>
     <row r="24" spans="2:17" x14ac:dyDescent="0.25">
@@ -1764,18 +1758,18 @@
         <v>9</v>
       </c>
       <c r="P24" t="s">
-        <v>68</v>
+        <v>132</v>
       </c>
     </row>
     <row r="25" spans="2:17" x14ac:dyDescent="0.25">
       <c r="N25" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O25">
         <v>10</v>
       </c>
       <c r="P25" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="26" spans="2:17" x14ac:dyDescent="0.25">
@@ -1783,7 +1777,7 @@
         <v>11</v>
       </c>
       <c r="P26" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27" spans="2:17" x14ac:dyDescent="0.25">
@@ -1791,7 +1785,7 @@
         <v>12</v>
       </c>
       <c r="P27" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28" spans="2:17" x14ac:dyDescent="0.25">
@@ -1799,37 +1793,34 @@
         <v>13</v>
       </c>
       <c r="P28" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="N29" t="s">
-        <v>97</v>
-      </c>
       <c r="O29">
         <v>14</v>
       </c>
       <c r="P29" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="30" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C30" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="O30">
         <v>15</v>
       </c>
       <c r="P30" t="s">
-        <v>61</v>
+        <v>133</v>
       </c>
     </row>
     <row r="31" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C31" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
@@ -1839,15 +1830,15 @@
         <v>16</v>
       </c>
       <c r="P31" t="s">
-        <v>98</v>
+        <v>134</v>
       </c>
     </row>
     <row r="32" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C32" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
@@ -1862,31 +1853,28 @@
     </row>
     <row r="33" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C33" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
       <c r="H33" s="6"/>
-      <c r="N33" t="s">
-        <v>97</v>
-      </c>
       <c r="O33">
         <v>18</v>
       </c>
       <c r="P33" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="34" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C34" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
@@ -1896,15 +1884,15 @@
         <v>19</v>
       </c>
       <c r="P34" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="35" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C35" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
@@ -1914,15 +1902,15 @@
         <v>20</v>
       </c>
       <c r="P35" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="36" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C36" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
@@ -1932,15 +1920,15 @@
         <v>21</v>
       </c>
       <c r="P36" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="37" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C37" t="s">
+        <v>121</v>
+      </c>
+      <c r="D37" s="6" t="s">
         <v>125</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>129</v>
       </c>
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
@@ -1950,18 +1938,15 @@
         <v>22</v>
       </c>
       <c r="P37" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="38" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="N38" t="s">
-        <v>97</v>
-      </c>
       <c r="O38">
         <v>23</v>
       </c>
       <c r="P38" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="39" spans="3:16" x14ac:dyDescent="0.25">
@@ -1969,7 +1954,7 @@
         <v>24</v>
       </c>
       <c r="P39" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="40" spans="3:16" x14ac:dyDescent="0.25">
@@ -2069,10 +2054,10 @@
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D1" s="8"/>
       <c r="E1" s="8"/>
@@ -2083,13 +2068,13 @@
     </row>
     <row r="2" spans="1:12" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
@@ -2098,16 +2083,16 @@
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
       <c r="L2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="10" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -2116,16 +2101,16 @@
       <c r="H3" s="9"/>
       <c r="I3" s="9"/>
       <c r="L3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="10" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -2134,18 +2119,18 @@
       <c r="H4" s="9"/>
       <c r="I4" s="9"/>
       <c r="L4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
@@ -2154,16 +2139,16 @@
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
       <c r="L5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="10" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
@@ -2174,11 +2159,11 @@
     </row>
     <row r="7" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="10" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
@@ -2189,13 +2174,13 @@
     </row>
     <row r="8" spans="1:12" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B8" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8" s="10" t="s">
         <v>86</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>88</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
@@ -2206,11 +2191,11 @@
     </row>
     <row r="9" spans="1:12" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="10" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
@@ -2221,11 +2206,11 @@
     </row>
     <row r="10" spans="1:12" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B10" s="8"/>
       <c r="C10" s="10" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
@@ -2236,13 +2221,13 @@
     </row>
     <row r="11" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
@@ -2253,11 +2238,11 @@
     </row>
     <row r="12" spans="1:12" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="10" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
@@ -2268,11 +2253,11 @@
     </row>
     <row r="13" spans="1:12" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="10" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
@@ -2283,7 +2268,7 @@
     </row>
     <row r="18" spans="13:18" x14ac:dyDescent="0.25">
       <c r="M18" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="19" spans="13:18" x14ac:dyDescent="0.25">
@@ -2302,50 +2287,50 @@
     </row>
     <row r="20" spans="13:18" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M20" t="s">
+        <v>97</v>
+      </c>
+      <c r="O20" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="P20" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="O20" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="P20" s="12" t="s">
-        <v>105</v>
-      </c>
       <c r="Q20" s="12" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="R20" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="13:18" x14ac:dyDescent="0.25">
       <c r="N23" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="O23" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="P23" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="Q23" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24" spans="13:18" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M24" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="N24" s="12" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="O24" s="12" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="P24" s="12" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="Q24" s="12" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/card disdoc.xlsx
+++ b/card disdoc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5a34dfa97c331738/Documents/ilja/Unity/ld60/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="223" documentId="8_{0C438EE4-F750-43B6-8F91-DB4328E051E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F086FD1-4C0D-4E33-8082-7A3DE68E6FD3}"/>
+  <xr:revisionPtr revIDLastSave="229" documentId="8_{0C438EE4-F750-43B6-8F91-DB4328E051E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FEF9B190-BCD8-49FE-A2F3-5A2B213E2B0A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{B625C734-B299-4013-86DD-D50F51382B50}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="138">
   <si>
     <t>Hand (pts)</t>
   </si>
@@ -220,9 +220,6 @@
   </si>
   <si>
     <t>206 / 204</t>
-  </si>
-  <si>
-    <t>odd dices grant bonus 0.2 multiplier</t>
   </si>
   <si>
     <t>you can destroy (right click) 6 to gain additional reroll and 0.5 multiplier</t>
@@ -563,6 +560,9 @@
     <t>change</t>
   </si>
   <si>
+    <t>new</t>
+  </si>
+  <si>
     <t>1 1 1 1 grants additoinal 200 points</t>
   </si>
   <si>
@@ -706,7 +706,13 @@
     <t>each 3 4 grants bonus 0.5 multiplier</t>
   </si>
   <si>
-    <t>straight grants 1 multiplier</t>
+    <t>straight grants 1.67 multiplier</t>
+  </si>
+  <si>
+    <t>2 4 6 grants 1 multiplier</t>
+  </si>
+  <si>
+    <t>each even dice grant 0.1 multiplier</t>
   </si>
 </sst>
 </file>
@@ -1655,7 +1661,7 @@
         <v>4</v>
       </c>
       <c r="P19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q19" t="s">
         <v>36</v>
@@ -1763,7 +1769,7 @@
     </row>
     <row r="25" spans="2:17" x14ac:dyDescent="0.25">
       <c r="N25" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O25">
         <v>10</v>
@@ -1777,7 +1783,7 @@
         <v>11</v>
       </c>
       <c r="P26" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="27" spans="2:17" x14ac:dyDescent="0.25">
@@ -1785,7 +1791,7 @@
         <v>12</v>
       </c>
       <c r="P27" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="28" spans="2:17" x14ac:dyDescent="0.25">
@@ -1793,7 +1799,7 @@
         <v>13</v>
       </c>
       <c r="P28" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" spans="2:17" x14ac:dyDescent="0.25">
@@ -1844,11 +1850,14 @@
       <c r="F32" s="6"/>
       <c r="G32" s="6"/>
       <c r="H32" s="6"/>
+      <c r="N32" t="s">
+        <v>93</v>
+      </c>
       <c r="O32">
         <v>17</v>
       </c>
       <c r="P32" t="s">
-        <v>60</v>
+        <v>137</v>
       </c>
     </row>
     <row r="33" spans="3:16" x14ac:dyDescent="0.25">
@@ -1884,7 +1893,7 @@
         <v>19</v>
       </c>
       <c r="P34" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="35" spans="3:16" x14ac:dyDescent="0.25">
@@ -1920,7 +1929,7 @@
         <v>21</v>
       </c>
       <c r="P36" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="37" spans="3:16" x14ac:dyDescent="0.25">
@@ -1938,7 +1947,7 @@
         <v>22</v>
       </c>
       <c r="P37" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="38" spans="3:16" x14ac:dyDescent="0.25">
@@ -1954,12 +1963,18 @@
         <v>24</v>
       </c>
       <c r="P39" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="40" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="N40" t="s">
+        <v>94</v>
+      </c>
       <c r="O40">
         <v>25</v>
+      </c>
+      <c r="P40" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="41" spans="3:16" x14ac:dyDescent="0.25">
@@ -2054,10 +2069,10 @@
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D1" s="8"/>
       <c r="E1" s="8"/>
@@ -2068,13 +2083,13 @@
     </row>
     <row r="2" spans="1:12" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
@@ -2083,16 +2098,16 @@
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
       <c r="L2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -2101,16 +2116,16 @@
       <c r="H3" s="9"/>
       <c r="I3" s="9"/>
       <c r="L3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -2119,18 +2134,18 @@
       <c r="H4" s="9"/>
       <c r="I4" s="9"/>
       <c r="L4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
@@ -2139,16 +2154,16 @@
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
       <c r="L5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
@@ -2159,11 +2174,11 @@
     </row>
     <row r="7" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
@@ -2174,13 +2189,13 @@
     </row>
     <row r="8" spans="1:12" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
@@ -2191,11 +2206,11 @@
     </row>
     <row r="9" spans="1:12" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
@@ -2206,11 +2221,11 @@
     </row>
     <row r="10" spans="1:12" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B10" s="8"/>
       <c r="C10" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
@@ -2221,13 +2236,13 @@
     </row>
     <row r="11" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
@@ -2238,11 +2253,11 @@
     </row>
     <row r="12" spans="1:12" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
@@ -2253,11 +2268,11 @@
     </row>
     <row r="13" spans="1:12" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>

--- a/card disdoc.xlsx
+++ b/card disdoc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5a34dfa97c331738/Documents/ilja/Unity/ld60/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="229" documentId="8_{0C438EE4-F750-43B6-8F91-DB4328E051E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FEF9B190-BCD8-49FE-A2F3-5A2B213E2B0A}"/>
+  <xr:revisionPtr revIDLastSave="232" documentId="8_{0C438EE4-F750-43B6-8F91-DB4328E051E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94F176CC-AE48-4219-B4B7-3478BDCAAE9D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{B625C734-B299-4013-86DD-D50F51382B50}"/>
   </bookViews>
@@ -712,7 +712,7 @@
     <t>2 4 6 grants 1 multiplier</t>
   </si>
   <si>
-    <t>each even dice grant 0.1 multiplier</t>
+    <t>each even dice grant 0.15 multiplier</t>
   </si>
 </sst>
 </file>

--- a/card disdoc.xlsx
+++ b/card disdoc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5a34dfa97c331738/Documents/ilja/Unity/ld60/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="232" documentId="8_{0C438EE4-F750-43B6-8F91-DB4328E051E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94F176CC-AE48-4219-B4B7-3478BDCAAE9D}"/>
+  <xr:revisionPtr revIDLastSave="257" documentId="8_{0C438EE4-F750-43B6-8F91-DB4328E051E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7331AE6-9119-42DF-A8AA-71FF626B836A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{B625C734-B299-4013-86DD-D50F51382B50}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="135">
   <si>
     <t>Hand (pts)</t>
   </si>
@@ -156,15 +156,6 @@
     <t xml:space="preserve">you can flip (right click) 2 to gain 5 and wiseverse any number of times </t>
   </si>
   <si>
-    <t>gain aditional reroll</t>
-  </si>
-  <si>
-    <t>gain additional dice. Loose 1 reroll</t>
-  </si>
-  <si>
-    <t>1 1 grants 52 bonus points</t>
-  </si>
-  <si>
     <t>44 / 44</t>
   </si>
   <si>
@@ -228,9 +219,6 @@
     <t>full house grants bonus 100 points</t>
   </si>
   <si>
-    <t>five of a kind grants bonus 333 points</t>
-  </si>
-  <si>
     <t>6 6 6 grants bonus 100 points</t>
   </si>
   <si>
@@ -238,9 +226,6 @@
   </si>
   <si>
     <t>4 4 4 grants bonus 100 points</t>
-  </si>
-  <si>
-    <t>1 2 3 grants 50 points and 1 additional reroll next round</t>
   </si>
   <si>
     <t xml:space="preserve">Speaker </t>
@@ -560,9 +545,6 @@
     <t>change</t>
   </si>
   <si>
-    <t>new</t>
-  </si>
-  <si>
     <t>1 1 1 1 grants additoinal 200 points</t>
   </si>
   <si>
@@ -713,6 +695,15 @@
   </si>
   <si>
     <t>each even dice grant 0.15 multiplier</t>
+  </si>
+  <si>
+    <t>five of a kind grants bonus 167 points</t>
+  </si>
+  <si>
+    <t>1 1 grants 33 bonus points</t>
+  </si>
+  <si>
+    <t>1 2 3 grants 67 points</t>
   </si>
 </sst>
 </file>
@@ -1604,16 +1595,13 @@
       <c r="O15">
         <v>0</v>
       </c>
-      <c r="P15" t="s">
-        <v>38</v>
-      </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="O16">
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.25">
@@ -1641,7 +1629,7 @@
         <v>3</v>
       </c>
       <c r="P18" t="s">
-        <v>40</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.25">
@@ -1649,19 +1637,19 @@
         <v>0</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="O19">
         <v>4</v>
       </c>
       <c r="P19" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="Q19" t="s">
         <v>36</v>
@@ -1672,13 +1660,13 @@
         <v>1</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="O20">
         <v>5</v>
@@ -1692,39 +1680,36 @@
         <v>2</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="O21">
         <v>6</v>
       </c>
       <c r="P21" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="22" spans="2:17" ht="30" x14ac:dyDescent="0.25">
       <c r="B22" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="O22">
         <v>7</v>
-      </c>
-      <c r="P22" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="23" spans="2:17" x14ac:dyDescent="0.25">
@@ -1732,19 +1717,19 @@
         <v>4</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="O23">
         <v>8</v>
       </c>
       <c r="P23" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="24" spans="2:17" x14ac:dyDescent="0.25">
@@ -1752,30 +1737,27 @@
         <v>5</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O24">
         <v>9</v>
       </c>
       <c r="P24" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="25" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="N25" t="s">
-        <v>93</v>
-      </c>
       <c r="O25">
         <v>10</v>
       </c>
       <c r="P25" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
     </row>
     <row r="26" spans="2:17" x14ac:dyDescent="0.25">
@@ -1783,7 +1765,7 @@
         <v>11</v>
       </c>
       <c r="P26" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27" spans="2:17" x14ac:dyDescent="0.25">
@@ -1791,7 +1773,7 @@
         <v>12</v>
       </c>
       <c r="P27" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" spans="2:17" x14ac:dyDescent="0.25">
@@ -1799,7 +1781,7 @@
         <v>13</v>
       </c>
       <c r="P28" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="29" spans="2:17" x14ac:dyDescent="0.25">
@@ -1807,26 +1789,26 @@
         <v>14</v>
       </c>
       <c r="P29" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="30" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C30" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="O30">
         <v>15</v>
       </c>
       <c r="P30" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="31" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C31" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
@@ -1836,36 +1818,33 @@
         <v>16</v>
       </c>
       <c r="P31" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
     </row>
     <row r="32" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C32" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
       <c r="G32" s="6"/>
       <c r="H32" s="6"/>
-      <c r="N32" t="s">
-        <v>93</v>
-      </c>
       <c r="O32">
         <v>17</v>
       </c>
       <c r="P32" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="33" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C33" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
@@ -1875,15 +1854,15 @@
         <v>18</v>
       </c>
       <c r="P33" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="34" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C34" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
@@ -1893,15 +1872,15 @@
         <v>19</v>
       </c>
       <c r="P34" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="35" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C35" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
@@ -1911,15 +1890,15 @@
         <v>20</v>
       </c>
       <c r="P35" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C36" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
@@ -1929,25 +1908,28 @@
         <v>21</v>
       </c>
       <c r="P36" t="s">
-        <v>62</v>
+        <v>132</v>
       </c>
     </row>
     <row r="37" spans="3:16" x14ac:dyDescent="0.25">
       <c r="C37" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
       <c r="G37" s="6"/>
       <c r="H37" s="6"/>
+      <c r="N37" t="s">
+        <v>88</v>
+      </c>
       <c r="O37">
         <v>22</v>
       </c>
       <c r="P37" t="s">
-        <v>66</v>
+        <v>134</v>
       </c>
     </row>
     <row r="38" spans="3:16" x14ac:dyDescent="0.25">
@@ -1955,7 +1937,7 @@
         <v>23</v>
       </c>
       <c r="P38" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
     </row>
     <row r="39" spans="3:16" x14ac:dyDescent="0.25">
@@ -1963,18 +1945,15 @@
         <v>24</v>
       </c>
       <c r="P39" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="40" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="N40" t="s">
-        <v>94</v>
-      </c>
       <c r="O40">
         <v>25</v>
       </c>
       <c r="P40" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="41" spans="3:16" x14ac:dyDescent="0.25">
@@ -2069,10 +2048,10 @@
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="7"/>
       <c r="B1" s="7" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D1" s="8"/>
       <c r="E1" s="8"/>
@@ -2083,13 +2062,13 @@
     </row>
     <row r="2" spans="1:12" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
@@ -2098,16 +2077,16 @@
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
       <c r="L2" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="10" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -2116,16 +2095,16 @@
       <c r="H3" s="9"/>
       <c r="I3" s="9"/>
       <c r="L3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="10" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -2134,18 +2113,18 @@
       <c r="H4" s="9"/>
       <c r="I4" s="9"/>
       <c r="L4" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>73</v>
-      </c>
       <c r="C5" s="10" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
@@ -2154,16 +2133,16 @@
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
       <c r="L5" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="10" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
@@ -2174,11 +2153,11 @@
     </row>
     <row r="7" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="10" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
@@ -2189,13 +2168,13 @@
     </row>
     <row r="8" spans="1:12" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
@@ -2206,11 +2185,11 @@
     </row>
     <row r="9" spans="1:12" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="10" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
@@ -2221,11 +2200,11 @@
     </row>
     <row r="10" spans="1:12" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B10" s="8"/>
       <c r="C10" s="10" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
@@ -2236,13 +2215,13 @@
     </row>
     <row r="11" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
@@ -2253,11 +2232,11 @@
     </row>
     <row r="12" spans="1:12" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="10" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
@@ -2268,11 +2247,11 @@
     </row>
     <row r="13" spans="1:12" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="10" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
@@ -2283,7 +2262,7 @@
     </row>
     <row r="18" spans="13:18" x14ac:dyDescent="0.25">
       <c r="M18" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="13:18" x14ac:dyDescent="0.25">
@@ -2302,50 +2281,50 @@
     </row>
     <row r="20" spans="13:18" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M20" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="O20" s="12" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="P20" s="12" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="Q20" s="12" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="R20" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" spans="13:18" x14ac:dyDescent="0.25">
       <c r="N23" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="O23" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="P23" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="Q23" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="13:18" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M24" t="s">
+        <v>96</v>
+      </c>
+      <c r="N24" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="N24" s="12" t="s">
-        <v>108</v>
-      </c>
       <c r="O24" s="12" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="P24" s="12" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="Q24" s="12" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
